--- a/docs/mv/MV-Manual.xlsx
+++ b/docs/mv/MV-Manual.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1403F2-61E9-41AB-99DC-B12B60BC1D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -26,7 +25,7 @@
     <definedName name="MmExcelLinker_36B46675_5644_4776_8F54_A7FD32C28D8E">cannot create top [1]mv!$D$9:$D$9</definedName>
     <definedName name="MmExcelLinker_B57A93C7_33C0_4A05_954D_5E613EE45F06">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,12 +41,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="C331" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="C331" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -76,12 +75,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="C15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="C19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="G66" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -148,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="1282">
   <si>
     <t>Manual TestList</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6718,7 +6717,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>的时候，用户登陆只能看见自己组织的</t>
+      <t>的时候，普通组织的用户登陆只能看见自己组织的</t>
     </r>
     <r>
       <rPr>
@@ -6737,7 +6736,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>数据，包括</t>
+      <t>数据，</t>
     </r>
     <r>
       <rPr>
@@ -6753,19 +6752,101 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="1"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>，不能切换组织</t>
+      <t>可以切换组织，查看操作其他组织的mv</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>//</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没有设置的时候，如果只有一个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>org administrator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，默认显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，如果有多个，默认显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>organization administrator role</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="51" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7095,13 +7176,6 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="1"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -8283,11 +8357,191 @@
     <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="5" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8295,24 +8549,6 @@
     <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="39" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -8325,181 +8561,55 @@
     <xf numFmtId="49" fontId="36" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="5" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8511,19 +8621,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -8538,36 +8636,102 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8583,123 +8747,33 @@
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="常规 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 3" xfId="2"/>
+    <cellStyle name="常规 5" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -9336,23 +9410,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -9388,23 +9445,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -9580,7 +9620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9815,7 +9855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q432"/>
   <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -10289,12 +10329,12 @@
       <c r="H36" s="300"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B37" s="304" t="s">
+      <c r="B37" s="308" t="s">
         <v>1262</v>
       </c>
-      <c r="C37" s="304"/>
-      <c r="D37" s="305"/>
-      <c r="E37" s="305"/>
+      <c r="C37" s="308"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
       <c r="F37" s="138" t="s">
         <v>328</v>
       </c>
@@ -10302,27 +10342,27 @@
       <c r="H37" s="136"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B38" s="304" t="s">
+      <c r="B38" s="308" t="s">
         <v>1263</v>
       </c>
-      <c r="C38" s="304"/>
-      <c r="D38" s="304" t="s">
+      <c r="C38" s="308"/>
+      <c r="D38" s="308" t="s">
         <v>1264</v>
       </c>
-      <c r="E38" s="304"/>
+      <c r="E38" s="308"/>
       <c r="F38" s="143"/>
       <c r="G38" s="144"/>
       <c r="H38" s="145"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="B39" s="304" t="s">
+      <c r="B39" s="308" t="s">
         <v>1265</v>
       </c>
-      <c r="C39" s="304"/>
-      <c r="D39" s="304" t="s">
+      <c r="C39" s="308"/>
+      <c r="D39" s="308" t="s">
         <v>1266</v>
       </c>
-      <c r="E39" s="304"/>
+      <c r="E39" s="308"/>
       <c r="F39" s="298" t="s">
         <v>329</v>
       </c>
@@ -10416,11 +10456,11 @@
         <v>309</v>
       </c>
       <c r="D48" s="172"/>
-      <c r="E48" s="311" t="s">
+      <c r="E48" s="356" t="s">
         <v>336</v>
       </c>
-      <c r="F48" s="312"/>
-      <c r="G48" s="313"/>
+      <c r="F48" s="357"/>
+      <c r="G48" s="358"/>
       <c r="H48" s="168"/>
       <c r="J48" s="166"/>
       <c r="L48" s="166"/>
@@ -10428,15 +10468,15 @@
       <c r="O48" s="170"/>
     </row>
     <row r="49" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C49" s="306" t="s">
+      <c r="C49" s="366" t="s">
         <v>337</v>
       </c>
-      <c r="D49" s="307"/>
-      <c r="E49" s="314" t="s">
+      <c r="D49" s="367"/>
+      <c r="E49" s="368" t="s">
         <v>338</v>
       </c>
-      <c r="F49" s="315"/>
-      <c r="G49" s="316"/>
+      <c r="F49" s="369"/>
+      <c r="G49" s="370"/>
       <c r="H49" s="303" t="s">
         <v>1267</v>
       </c>
@@ -10447,15 +10487,15 @@
     </row>
     <row r="50" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="168"/>
-      <c r="C50" s="306" t="s">
+      <c r="C50" s="366" t="s">
         <v>339</v>
       </c>
-      <c r="D50" s="307"/>
-      <c r="E50" s="308" t="s">
+      <c r="D50" s="367"/>
+      <c r="E50" s="338" t="s">
         <v>340</v>
       </c>
-      <c r="F50" s="309"/>
-      <c r="G50" s="310"/>
+      <c r="F50" s="339"/>
+      <c r="G50" s="340"/>
       <c r="H50" s="168"/>
       <c r="I50" s="168"/>
       <c r="J50" s="166"/>
@@ -10486,11 +10526,11 @@
         <v>342</v>
       </c>
       <c r="D52" s="172"/>
-      <c r="E52" s="317" t="s">
+      <c r="E52" s="371" t="s">
         <v>336</v>
       </c>
-      <c r="F52" s="317"/>
-      <c r="G52" s="317"/>
+      <c r="F52" s="371"/>
+      <c r="G52" s="371"/>
       <c r="H52" s="168"/>
       <c r="J52" s="166"/>
       <c r="L52" s="166"/>
@@ -10498,15 +10538,15 @@
       <c r="O52" s="170"/>
     </row>
     <row r="53" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C53" s="306" t="s">
+      <c r="C53" s="366" t="s">
         <v>337</v>
       </c>
-      <c r="D53" s="307"/>
-      <c r="E53" s="308" t="s">
+      <c r="D53" s="367"/>
+      <c r="E53" s="338" t="s">
         <v>338</v>
       </c>
-      <c r="F53" s="309"/>
-      <c r="G53" s="310"/>
+      <c r="F53" s="339"/>
+      <c r="G53" s="340"/>
       <c r="H53" s="168"/>
       <c r="J53" s="166"/>
       <c r="L53" s="166"/>
@@ -10515,15 +10555,15 @@
     </row>
     <row r="54" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B54" s="168"/>
-      <c r="C54" s="306" t="s">
+      <c r="C54" s="366" t="s">
         <v>339</v>
       </c>
-      <c r="D54" s="307"/>
-      <c r="E54" s="308" t="s">
+      <c r="D54" s="367"/>
+      <c r="E54" s="338" t="s">
         <v>340</v>
       </c>
-      <c r="F54" s="309"/>
-      <c r="G54" s="310"/>
+      <c r="F54" s="339"/>
+      <c r="G54" s="340"/>
       <c r="H54" s="168"/>
       <c r="I54" s="168"/>
       <c r="J54" s="166"/>
@@ -10568,145 +10608,145 @@
         <v>707</v>
       </c>
       <c r="C57" s="164"/>
-      <c r="D57" s="306" t="s">
+      <c r="D57" s="366" t="s">
         <v>309</v>
       </c>
-      <c r="E57" s="307"/>
-      <c r="F57" s="311" t="s">
+      <c r="E57" s="367"/>
+      <c r="F57" s="356" t="s">
         <v>336</v>
       </c>
-      <c r="G57" s="312"/>
-      <c r="H57" s="312"/>
-      <c r="I57" s="312"/>
-      <c r="J57" s="312"/>
-      <c r="K57" s="312"/>
-      <c r="L57" s="312"/>
-      <c r="M57" s="312"/>
-      <c r="N57" s="313"/>
+      <c r="G57" s="357"/>
+      <c r="H57" s="357"/>
+      <c r="I57" s="357"/>
+      <c r="J57" s="357"/>
+      <c r="K57" s="357"/>
+      <c r="L57" s="357"/>
+      <c r="M57" s="357"/>
+      <c r="N57" s="358"/>
       <c r="O57" s="170"/>
     </row>
     <row r="58" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="166"/>
-      <c r="C58" s="318" t="s">
+      <c r="C58" s="355" t="s">
         <v>345</v>
       </c>
-      <c r="D58" s="327" t="s">
+      <c r="D58" s="345" t="s">
         <v>337</v>
       </c>
-      <c r="E58" s="328"/>
-      <c r="F58" s="318" t="s">
+      <c r="E58" s="346"/>
+      <c r="F58" s="355" t="s">
         <v>346</v>
       </c>
-      <c r="G58" s="318"/>
-      <c r="H58" s="318"/>
-      <c r="I58" s="318"/>
-      <c r="J58" s="318"/>
-      <c r="K58" s="318"/>
-      <c r="L58" s="318"/>
-      <c r="M58" s="318"/>
-      <c r="N58" s="318"/>
+      <c r="G58" s="355"/>
+      <c r="H58" s="355"/>
+      <c r="I58" s="355"/>
+      <c r="J58" s="355"/>
+      <c r="K58" s="355"/>
+      <c r="L58" s="355"/>
+      <c r="M58" s="355"/>
+      <c r="N58" s="355"/>
       <c r="O58" s="173"/>
     </row>
     <row r="59" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="166"/>
-      <c r="C59" s="326"/>
-      <c r="D59" s="329"/>
-      <c r="E59" s="330"/>
-      <c r="F59" s="331" t="s">
+      <c r="C59" s="359"/>
+      <c r="D59" s="347"/>
+      <c r="E59" s="348"/>
+      <c r="F59" s="360" t="s">
         <v>347</v>
       </c>
-      <c r="G59" s="332"/>
-      <c r="H59" s="332"/>
-      <c r="I59" s="332"/>
-      <c r="J59" s="332"/>
-      <c r="K59" s="332"/>
-      <c r="L59" s="332"/>
-      <c r="M59" s="332"/>
-      <c r="N59" s="333"/>
+      <c r="G59" s="351"/>
+      <c r="H59" s="351"/>
+      <c r="I59" s="351"/>
+      <c r="J59" s="351"/>
+      <c r="K59" s="351"/>
+      <c r="L59" s="351"/>
+      <c r="M59" s="351"/>
+      <c r="N59" s="352"/>
       <c r="O59" s="174" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="60" spans="2:15" s="165" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="166"/>
-      <c r="C60" s="326"/>
-      <c r="D60" s="327" t="s">
+      <c r="C60" s="359"/>
+      <c r="D60" s="345" t="s">
         <v>339</v>
       </c>
-      <c r="E60" s="328"/>
-      <c r="F60" s="336" t="s">
+      <c r="E60" s="346"/>
+      <c r="F60" s="361" t="s">
         <v>349</v>
       </c>
-      <c r="G60" s="337"/>
-      <c r="H60" s="337"/>
-      <c r="I60" s="337"/>
-      <c r="J60" s="337"/>
-      <c r="K60" s="337"/>
-      <c r="L60" s="337"/>
-      <c r="M60" s="337"/>
-      <c r="N60" s="338"/>
+      <c r="G60" s="362"/>
+      <c r="H60" s="362"/>
+      <c r="I60" s="362"/>
+      <c r="J60" s="362"/>
+      <c r="K60" s="362"/>
+      <c r="L60" s="362"/>
+      <c r="M60" s="362"/>
+      <c r="N60" s="363"/>
       <c r="O60" s="173"/>
     </row>
     <row r="61" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="166"/>
-      <c r="C61" s="319"/>
-      <c r="D61" s="334"/>
-      <c r="E61" s="335"/>
-      <c r="F61" s="339" t="s">
+      <c r="C61" s="353"/>
+      <c r="D61" s="349"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="364" t="s">
         <v>350</v>
       </c>
-      <c r="G61" s="340"/>
-      <c r="H61" s="340"/>
-      <c r="I61" s="340"/>
-      <c r="J61" s="340"/>
-      <c r="K61" s="340"/>
-      <c r="L61" s="340"/>
-      <c r="M61" s="340"/>
-      <c r="N61" s="340"/>
+      <c r="G61" s="365"/>
+      <c r="H61" s="365"/>
+      <c r="I61" s="365"/>
+      <c r="J61" s="365"/>
+      <c r="K61" s="365"/>
+      <c r="L61" s="365"/>
+      <c r="M61" s="365"/>
+      <c r="N61" s="365"/>
       <c r="O61" s="174" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="62" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="166"/>
-      <c r="C62" s="318" t="s">
+      <c r="C62" s="355" t="s">
         <v>351</v>
       </c>
-      <c r="D62" s="320" t="s">
+      <c r="D62" s="372" t="s">
         <v>307</v>
       </c>
-      <c r="E62" s="321"/>
-      <c r="F62" s="322" t="s">
+      <c r="E62" s="373"/>
+      <c r="F62" s="354" t="s">
         <v>352</v>
       </c>
-      <c r="G62" s="322"/>
-      <c r="H62" s="322"/>
-      <c r="I62" s="322"/>
-      <c r="J62" s="322"/>
-      <c r="K62" s="322"/>
-      <c r="L62" s="322"/>
-      <c r="M62" s="322"/>
-      <c r="N62" s="322"/>
+      <c r="G62" s="354"/>
+      <c r="H62" s="354"/>
+      <c r="I62" s="354"/>
+      <c r="J62" s="354"/>
+      <c r="K62" s="354"/>
+      <c r="L62" s="354"/>
+      <c r="M62" s="354"/>
+      <c r="N62" s="354"/>
       <c r="O62" s="170"/>
     </row>
     <row r="63" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="166"/>
-      <c r="C63" s="319"/>
-      <c r="D63" s="323" t="s">
+      <c r="C63" s="353"/>
+      <c r="D63" s="374" t="s">
         <v>339</v>
       </c>
-      <c r="E63" s="324"/>
-      <c r="F63" s="325" t="s">
+      <c r="E63" s="375"/>
+      <c r="F63" s="376" t="s">
         <v>352</v>
       </c>
-      <c r="G63" s="325"/>
-      <c r="H63" s="325"/>
-      <c r="I63" s="325"/>
-      <c r="J63" s="325"/>
-      <c r="K63" s="325"/>
-      <c r="L63" s="325"/>
-      <c r="M63" s="325"/>
-      <c r="N63" s="325"/>
+      <c r="G63" s="376"/>
+      <c r="H63" s="376"/>
+      <c r="I63" s="376"/>
+      <c r="J63" s="376"/>
+      <c r="K63" s="376"/>
+      <c r="L63" s="376"/>
+      <c r="M63" s="376"/>
+      <c r="N63" s="376"/>
       <c r="O63" s="170"/>
     </row>
     <row r="64" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
@@ -10730,50 +10770,50 @@
         <v>353</v>
       </c>
       <c r="C65" s="167"/>
-      <c r="D65" s="318" t="s">
+      <c r="D65" s="355" t="s">
         <v>354</v>
       </c>
-      <c r="E65" s="318"/>
-      <c r="F65" s="311" t="s">
+      <c r="E65" s="355"/>
+      <c r="F65" s="356" t="s">
         <v>336</v>
       </c>
-      <c r="G65" s="312"/>
-      <c r="H65" s="312"/>
-      <c r="I65" s="312"/>
-      <c r="J65" s="312"/>
-      <c r="K65" s="312"/>
-      <c r="L65" s="312"/>
-      <c r="M65" s="312"/>
-      <c r="N65" s="313"/>
+      <c r="G65" s="357"/>
+      <c r="H65" s="357"/>
+      <c r="I65" s="357"/>
+      <c r="J65" s="357"/>
+      <c r="K65" s="357"/>
+      <c r="L65" s="357"/>
+      <c r="M65" s="357"/>
+      <c r="N65" s="358"/>
       <c r="O65" s="170"/>
     </row>
     <row r="66" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="166"/>
-      <c r="C66" s="346" t="s">
+      <c r="C66" s="344" t="s">
         <v>355</v>
       </c>
-      <c r="D66" s="327" t="s">
+      <c r="D66" s="345" t="s">
         <v>307</v>
       </c>
-      <c r="E66" s="328"/>
-      <c r="F66" s="309" t="s">
+      <c r="E66" s="346"/>
+      <c r="F66" s="339" t="s">
         <v>356</v>
       </c>
-      <c r="G66" s="309"/>
-      <c r="H66" s="309"/>
-      <c r="I66" s="309"/>
-      <c r="J66" s="309"/>
-      <c r="K66" s="309"/>
-      <c r="L66" s="309"/>
-      <c r="M66" s="309"/>
-      <c r="N66" s="310"/>
+      <c r="G66" s="339"/>
+      <c r="H66" s="339"/>
+      <c r="I66" s="339"/>
+      <c r="J66" s="339"/>
+      <c r="K66" s="339"/>
+      <c r="L66" s="339"/>
+      <c r="M66" s="339"/>
+      <c r="N66" s="340"/>
       <c r="O66" s="173"/>
     </row>
     <row r="67" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B67" s="166"/>
-      <c r="C67" s="346"/>
-      <c r="D67" s="329"/>
-      <c r="E67" s="330"/>
+      <c r="C67" s="344"/>
+      <c r="D67" s="347"/>
+      <c r="E67" s="348"/>
       <c r="F67" s="296" t="s">
         <v>357</v>
       </c>
@@ -10791,11 +10831,11 @@
     </row>
     <row r="68" spans="2:15" s="165" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="166"/>
-      <c r="C68" s="346"/>
-      <c r="D68" s="327" t="s">
+      <c r="C68" s="344"/>
+      <c r="D68" s="345" t="s">
         <v>339</v>
       </c>
-      <c r="E68" s="328"/>
+      <c r="E68" s="346"/>
       <c r="F68" s="293" t="s">
         <v>358</v>
       </c>
@@ -10811,106 +10851,106 @@
     </row>
     <row r="69" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="166"/>
-      <c r="C69" s="346"/>
-      <c r="D69" s="334"/>
-      <c r="E69" s="335"/>
-      <c r="F69" s="332" t="s">
+      <c r="C69" s="344"/>
+      <c r="D69" s="349"/>
+      <c r="E69" s="350"/>
+      <c r="F69" s="351" t="s">
         <v>347</v>
       </c>
-      <c r="G69" s="332"/>
-      <c r="H69" s="332"/>
-      <c r="I69" s="332"/>
-      <c r="J69" s="332"/>
-      <c r="K69" s="332"/>
-      <c r="L69" s="332"/>
-      <c r="M69" s="332"/>
-      <c r="N69" s="333"/>
+      <c r="G69" s="351"/>
+      <c r="H69" s="351"/>
+      <c r="I69" s="351"/>
+      <c r="J69" s="351"/>
+      <c r="K69" s="351"/>
+      <c r="L69" s="351"/>
+      <c r="M69" s="351"/>
+      <c r="N69" s="352"/>
       <c r="O69" s="174" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="70" spans="2:15" s="165" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="166"/>
-      <c r="C70" s="341" t="s">
+      <c r="C70" s="336" t="s">
         <v>359</v>
       </c>
-      <c r="D70" s="319" t="s">
+      <c r="D70" s="353" t="s">
         <v>337</v>
       </c>
-      <c r="E70" s="319"/>
-      <c r="F70" s="308" t="s">
+      <c r="E70" s="353"/>
+      <c r="F70" s="338" t="s">
         <v>360</v>
       </c>
-      <c r="G70" s="309"/>
-      <c r="H70" s="309"/>
-      <c r="I70" s="309"/>
-      <c r="J70" s="309"/>
-      <c r="K70" s="309"/>
-      <c r="L70" s="309"/>
-      <c r="M70" s="309"/>
-      <c r="N70" s="310"/>
+      <c r="G70" s="339"/>
+      <c r="H70" s="339"/>
+      <c r="I70" s="339"/>
+      <c r="J70" s="339"/>
+      <c r="K70" s="339"/>
+      <c r="L70" s="339"/>
+      <c r="M70" s="339"/>
+      <c r="N70" s="340"/>
       <c r="O70" s="170"/>
     </row>
     <row r="71" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B71" s="166"/>
-      <c r="C71" s="341"/>
-      <c r="D71" s="322" t="s">
+      <c r="C71" s="336"/>
+      <c r="D71" s="354" t="s">
         <v>181</v>
       </c>
-      <c r="E71" s="322"/>
-      <c r="F71" s="308" t="s">
+      <c r="E71" s="354"/>
+      <c r="F71" s="338" t="s">
         <v>360</v>
       </c>
-      <c r="G71" s="309"/>
-      <c r="H71" s="309"/>
-      <c r="I71" s="309"/>
-      <c r="J71" s="309"/>
-      <c r="K71" s="309"/>
-      <c r="L71" s="309"/>
-      <c r="M71" s="309"/>
-      <c r="N71" s="310"/>
+      <c r="G71" s="339"/>
+      <c r="H71" s="339"/>
+      <c r="I71" s="339"/>
+      <c r="J71" s="339"/>
+      <c r="K71" s="339"/>
+      <c r="L71" s="339"/>
+      <c r="M71" s="339"/>
+      <c r="N71" s="340"/>
       <c r="O71" s="170"/>
     </row>
     <row r="72" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="166"/>
-      <c r="C72" s="341" t="s">
+      <c r="C72" s="336" t="s">
         <v>361</v>
       </c>
-      <c r="D72" s="342" t="s">
+      <c r="D72" s="337" t="s">
         <v>307</v>
       </c>
-      <c r="E72" s="342"/>
-      <c r="F72" s="308" t="s">
+      <c r="E72" s="337"/>
+      <c r="F72" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="G72" s="309"/>
-      <c r="H72" s="309"/>
-      <c r="I72" s="309"/>
-      <c r="J72" s="309"/>
-      <c r="K72" s="309"/>
-      <c r="L72" s="309"/>
-      <c r="M72" s="309"/>
-      <c r="N72" s="310"/>
+      <c r="G72" s="339"/>
+      <c r="H72" s="339"/>
+      <c r="I72" s="339"/>
+      <c r="J72" s="339"/>
+      <c r="K72" s="339"/>
+      <c r="L72" s="339"/>
+      <c r="M72" s="339"/>
+      <c r="N72" s="340"/>
       <c r="O72" s="170"/>
     </row>
     <row r="73" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B73" s="166"/>
-      <c r="C73" s="341"/>
-      <c r="D73" s="342" t="s">
+      <c r="C73" s="336"/>
+      <c r="D73" s="337" t="s">
         <v>181</v>
       </c>
-      <c r="E73" s="342"/>
-      <c r="F73" s="343" t="s">
+      <c r="E73" s="337"/>
+      <c r="F73" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="G73" s="344"/>
-      <c r="H73" s="344"/>
-      <c r="I73" s="344"/>
-      <c r="J73" s="344"/>
-      <c r="K73" s="344"/>
-      <c r="L73" s="344"/>
-      <c r="M73" s="344"/>
-      <c r="N73" s="345"/>
+      <c r="G73" s="342"/>
+      <c r="H73" s="342"/>
+      <c r="I73" s="342"/>
+      <c r="J73" s="342"/>
+      <c r="K73" s="342"/>
+      <c r="L73" s="342"/>
+      <c r="M73" s="342"/>
+      <c r="N73" s="343"/>
       <c r="O73" s="170"/>
     </row>
     <row r="74" spans="2:15" s="165" customFormat="1" x14ac:dyDescent="0.15">
@@ -10991,7 +11031,7 @@
         <v>1258</v>
       </c>
       <c r="C86" s="164"/>
-      <c r="G86" s="440" t="s">
+      <c r="G86" s="304" t="s">
         <v>1279</v>
       </c>
     </row>
@@ -11149,12 +11189,12 @@
       <c r="C109" s="292" t="s">
         <v>386</v>
       </c>
-      <c r="D109" s="304" t="s">
+      <c r="D109" s="308" t="s">
         <v>382</v>
       </c>
-      <c r="E109" s="304"/>
-      <c r="F109" s="304"/>
-      <c r="G109" s="304"/>
+      <c r="E109" s="308"/>
+      <c r="F109" s="308"/>
+      <c r="G109" s="308"/>
     </row>
     <row r="110" spans="2:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B110" s="292" t="s">
@@ -11163,12 +11203,12 @@
       <c r="C110" s="292" t="s">
         <v>1269</v>
       </c>
-      <c r="D110" s="304" t="s">
+      <c r="D110" s="308" t="s">
         <v>1270</v>
       </c>
-      <c r="E110" s="304"/>
-      <c r="F110" s="304"/>
-      <c r="G110" s="304"/>
+      <c r="E110" s="308"/>
+      <c r="F110" s="308"/>
+      <c r="G110" s="308"/>
     </row>
     <row r="111" spans="2:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B111" s="292" t="s">
@@ -11177,12 +11217,12 @@
       <c r="C111" s="292" t="s">
         <v>1271</v>
       </c>
-      <c r="D111" s="304" t="s">
+      <c r="D111" s="308" t="s">
         <v>1272</v>
       </c>
-      <c r="E111" s="304"/>
-      <c r="F111" s="304"/>
-      <c r="G111" s="304"/>
+      <c r="E111" s="308"/>
+      <c r="F111" s="308"/>
+      <c r="G111" s="308"/>
     </row>
     <row r="112" spans="2:15" collapsed="1" x14ac:dyDescent="0.15"/>
     <row r="113" spans="2:17" x14ac:dyDescent="0.15">
@@ -12107,61 +12147,61 @@
       </c>
     </row>
     <row r="210" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C210" s="304" t="s">
+      <c r="C210" s="308" t="s">
         <v>489</v>
       </c>
-      <c r="D210" s="304"/>
-      <c r="E210" s="304"/>
-      <c r="F210" s="347" t="s">
+      <c r="D210" s="308"/>
+      <c r="E210" s="308"/>
+      <c r="F210" s="331" t="s">
         <v>490</v>
       </c>
-      <c r="G210" s="348"/>
-      <c r="H210" s="348"/>
-      <c r="I210" s="348"/>
-      <c r="J210" s="348"/>
-      <c r="K210" s="348"/>
-      <c r="L210" s="348"/>
-      <c r="M210" s="349"/>
+      <c r="G210" s="332"/>
+      <c r="H210" s="332"/>
+      <c r="I210" s="332"/>
+      <c r="J210" s="332"/>
+      <c r="K210" s="332"/>
+      <c r="L210" s="332"/>
+      <c r="M210" s="333"/>
       <c r="O210" s="133" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="211" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C211" s="304" t="s">
+      <c r="C211" s="308" t="s">
         <v>492</v>
       </c>
-      <c r="D211" s="304"/>
-      <c r="E211" s="304"/>
-      <c r="F211" s="347" t="s">
+      <c r="D211" s="308"/>
+      <c r="E211" s="308"/>
+      <c r="F211" s="331" t="s">
         <v>493</v>
       </c>
-      <c r="G211" s="348"/>
-      <c r="H211" s="348"/>
-      <c r="I211" s="348"/>
-      <c r="J211" s="348"/>
-      <c r="K211" s="348"/>
-      <c r="L211" s="348"/>
-      <c r="M211" s="349"/>
+      <c r="G211" s="332"/>
+      <c r="H211" s="332"/>
+      <c r="I211" s="332"/>
+      <c r="J211" s="332"/>
+      <c r="K211" s="332"/>
+      <c r="L211" s="332"/>
+      <c r="M211" s="333"/>
       <c r="O211" s="133" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="212" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C212" s="304" t="s">
+      <c r="C212" s="308" t="s">
         <v>494</v>
       </c>
-      <c r="D212" s="304"/>
-      <c r="E212" s="304"/>
-      <c r="F212" s="347" t="s">
+      <c r="D212" s="308"/>
+      <c r="E212" s="308"/>
+      <c r="F212" s="331" t="s">
         <v>495</v>
       </c>
-      <c r="G212" s="348"/>
-      <c r="H212" s="348"/>
-      <c r="I212" s="348"/>
-      <c r="J212" s="348"/>
-      <c r="K212" s="348"/>
-      <c r="L212" s="348"/>
-      <c r="M212" s="349"/>
+      <c r="G212" s="332"/>
+      <c r="H212" s="332"/>
+      <c r="I212" s="332"/>
+      <c r="J212" s="332"/>
+      <c r="K212" s="332"/>
+      <c r="L212" s="332"/>
+      <c r="M212" s="333"/>
       <c r="O212" s="133" t="s">
         <v>491</v>
       </c>
@@ -12288,101 +12328,101 @@
       </c>
     </row>
     <row r="220" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C220" s="304" t="s">
+      <c r="C220" s="308" t="s">
         <v>500</v>
       </c>
-      <c r="D220" s="304"/>
-      <c r="E220" s="304"/>
-      <c r="F220" s="304" t="s">
+      <c r="D220" s="308"/>
+      <c r="E220" s="308"/>
+      <c r="F220" s="308" t="s">
         <v>501</v>
       </c>
-      <c r="G220" s="304"/>
-      <c r="H220" s="304"/>
-      <c r="I220" s="304"/>
-      <c r="J220" s="304"/>
-      <c r="K220" s="304"/>
-      <c r="L220" s="304"/>
-      <c r="M220" s="304"/>
+      <c r="G220" s="308"/>
+      <c r="H220" s="308"/>
+      <c r="I220" s="308"/>
+      <c r="J220" s="308"/>
+      <c r="K220" s="308"/>
+      <c r="L220" s="308"/>
+      <c r="M220" s="308"/>
       <c r="O220" s="133" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="221" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C221" s="304" t="s">
+      <c r="C221" s="308" t="s">
         <v>475</v>
       </c>
-      <c r="D221" s="304"/>
-      <c r="E221" s="304"/>
-      <c r="F221" s="304" t="s">
+      <c r="D221" s="308"/>
+      <c r="E221" s="308"/>
+      <c r="F221" s="308" t="s">
         <v>502</v>
       </c>
-      <c r="G221" s="304"/>
-      <c r="H221" s="304"/>
-      <c r="I221" s="304"/>
-      <c r="J221" s="304"/>
-      <c r="K221" s="304"/>
-      <c r="L221" s="304"/>
-      <c r="M221" s="304"/>
+      <c r="G221" s="308"/>
+      <c r="H221" s="308"/>
+      <c r="I221" s="308"/>
+      <c r="J221" s="308"/>
+      <c r="K221" s="308"/>
+      <c r="L221" s="308"/>
+      <c r="M221" s="308"/>
       <c r="O221" s="133" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="222" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C222" s="304" t="s">
+      <c r="C222" s="308" t="s">
         <v>503</v>
       </c>
-      <c r="D222" s="304"/>
-      <c r="E222" s="304"/>
-      <c r="F222" s="304" t="s">
+      <c r="D222" s="308"/>
+      <c r="E222" s="308"/>
+      <c r="F222" s="308" t="s">
         <v>504</v>
       </c>
-      <c r="G222" s="304"/>
-      <c r="H222" s="304"/>
-      <c r="I222" s="304"/>
-      <c r="J222" s="304"/>
-      <c r="K222" s="304"/>
-      <c r="L222" s="304"/>
-      <c r="M222" s="304"/>
+      <c r="G222" s="308"/>
+      <c r="H222" s="308"/>
+      <c r="I222" s="308"/>
+      <c r="J222" s="308"/>
+      <c r="K222" s="308"/>
+      <c r="L222" s="308"/>
+      <c r="M222" s="308"/>
       <c r="O222" s="133" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="223" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C223" s="304" t="s">
+      <c r="C223" s="308" t="s">
         <v>506</v>
       </c>
-      <c r="D223" s="304"/>
-      <c r="E223" s="304"/>
-      <c r="F223" s="304" t="s">
+      <c r="D223" s="308"/>
+      <c r="E223" s="308"/>
+      <c r="F223" s="308" t="s">
         <v>507</v>
       </c>
-      <c r="G223" s="304"/>
-      <c r="H223" s="304"/>
-      <c r="I223" s="304"/>
-      <c r="J223" s="304"/>
-      <c r="K223" s="304"/>
-      <c r="L223" s="304"/>
-      <c r="M223" s="304"/>
+      <c r="G223" s="308"/>
+      <c r="H223" s="308"/>
+      <c r="I223" s="308"/>
+      <c r="J223" s="308"/>
+      <c r="K223" s="308"/>
+      <c r="L223" s="308"/>
+      <c r="M223" s="308"/>
       <c r="O223" s="133" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="224" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="C224" s="355" t="s">
+      <c r="C224" s="335" t="s">
         <v>508</v>
       </c>
-      <c r="D224" s="355"/>
-      <c r="E224" s="355"/>
-      <c r="F224" s="355" t="s">
+      <c r="D224" s="335"/>
+      <c r="E224" s="335"/>
+      <c r="F224" s="335" t="s">
         <v>1045</v>
       </c>
-      <c r="G224" s="355"/>
-      <c r="H224" s="355"/>
-      <c r="I224" s="355"/>
-      <c r="J224" s="355"/>
-      <c r="K224" s="355"/>
-      <c r="L224" s="355"/>
-      <c r="M224" s="355"/>
+      <c r="G224" s="335"/>
+      <c r="H224" s="335"/>
+      <c r="I224" s="335"/>
+      <c r="J224" s="335"/>
+      <c r="K224" s="335"/>
+      <c r="L224" s="335"/>
+      <c r="M224" s="335"/>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B225" s="132" t="s">
@@ -12390,41 +12430,41 @@
       </c>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="C226" s="304" t="s">
+      <c r="C226" s="308" t="s">
         <v>510</v>
       </c>
-      <c r="D226" s="304"/>
-      <c r="E226" s="304"/>
-      <c r="F226" s="347" t="s">
+      <c r="D226" s="308"/>
+      <c r="E226" s="308"/>
+      <c r="F226" s="331" t="s">
         <v>511</v>
       </c>
-      <c r="G226" s="348"/>
-      <c r="H226" s="348"/>
-      <c r="I226" s="348"/>
-      <c r="J226" s="348"/>
-      <c r="K226" s="348"/>
-      <c r="L226" s="348"/>
-      <c r="M226" s="349"/>
+      <c r="G226" s="332"/>
+      <c r="H226" s="332"/>
+      <c r="I226" s="332"/>
+      <c r="J226" s="332"/>
+      <c r="K226" s="332"/>
+      <c r="L226" s="332"/>
+      <c r="M226" s="333"/>
       <c r="O226" s="133" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="C227" s="304" t="s">
+      <c r="C227" s="308" t="s">
         <v>513</v>
       </c>
-      <c r="D227" s="304"/>
-      <c r="E227" s="304"/>
-      <c r="F227" s="347" t="s">
+      <c r="D227" s="308"/>
+      <c r="E227" s="308"/>
+      <c r="F227" s="331" t="s">
         <v>514</v>
       </c>
-      <c r="G227" s="348"/>
-      <c r="H227" s="348"/>
-      <c r="I227" s="348"/>
-      <c r="J227" s="348"/>
-      <c r="K227" s="348"/>
-      <c r="L227" s="348"/>
-      <c r="M227" s="349"/>
+      <c r="G227" s="332"/>
+      <c r="H227" s="332"/>
+      <c r="I227" s="332"/>
+      <c r="J227" s="332"/>
+      <c r="K227" s="332"/>
+      <c r="L227" s="332"/>
+      <c r="M227" s="333"/>
       <c r="O227" s="133" t="s">
         <v>461</v>
       </c>
@@ -13033,10 +13073,10 @@
       </c>
     </row>
     <row r="290" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B290" s="350" t="s">
+      <c r="B290" s="327" t="s">
         <v>568</v>
       </c>
-      <c r="C290" s="351"/>
+      <c r="C290" s="334"/>
       <c r="D290" s="148" t="s">
         <v>569</v>
       </c>
@@ -13044,10 +13084,10 @@
       <c r="F290" s="301" t="s">
         <v>562</v>
       </c>
-      <c r="G290" s="352" t="s">
+      <c r="G290" s="310" t="s">
         <v>546</v>
       </c>
-      <c r="H290" s="352"/>
+      <c r="H290" s="310"/>
     </row>
     <row r="291" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B291" s="147" t="s">
@@ -13056,15 +13096,15 @@
       <c r="C291" s="147" t="s">
         <v>571</v>
       </c>
-      <c r="D291" s="353" t="s">
+      <c r="D291" s="318" t="s">
         <v>545</v>
       </c>
-      <c r="E291" s="353"/>
+      <c r="E291" s="318"/>
       <c r="F291" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G291" s="354"/>
-      <c r="H291" s="354"/>
+      <c r="G291" s="330"/>
+      <c r="H291" s="330"/>
       <c r="O291" s="133" t="s">
         <v>565</v>
       </c>
@@ -13076,30 +13116,30 @@
       <c r="C292" s="142" t="s">
         <v>572</v>
       </c>
-      <c r="D292" s="304" t="s">
+      <c r="D292" s="308" t="s">
         <v>572</v>
       </c>
-      <c r="E292" s="304"/>
+      <c r="E292" s="308"/>
       <c r="F292" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G292" s="354"/>
-      <c r="H292" s="354"/>
+      <c r="G292" s="330"/>
+      <c r="H292" s="330"/>
     </row>
     <row r="293" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B293" s="139"/>
       <c r="C293" s="142"/>
-      <c r="D293" s="304" t="s">
+      <c r="D293" s="308" t="s">
         <v>573</v>
       </c>
-      <c r="E293" s="304"/>
+      <c r="E293" s="308"/>
       <c r="F293" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G293" s="304" t="s">
+      <c r="G293" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H293" s="304"/>
+      <c r="H293" s="308"/>
     </row>
     <row r="294" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B294" s="137" t="s">
@@ -13108,17 +13148,17 @@
       <c r="C294" s="136" t="s">
         <v>572</v>
       </c>
-      <c r="D294" s="304" t="s">
+      <c r="D294" s="308" t="s">
         <v>573</v>
       </c>
-      <c r="E294" s="304"/>
+      <c r="E294" s="308"/>
       <c r="F294" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G294" s="304" t="s">
+      <c r="G294" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H294" s="304"/>
+      <c r="H294" s="308"/>
     </row>
     <row r="295" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B295" s="137" t="s">
@@ -13127,32 +13167,32 @@
       <c r="C295" s="136" t="s">
         <v>573</v>
       </c>
-      <c r="D295" s="304" t="s">
+      <c r="D295" s="308" t="s">
         <v>574</v>
       </c>
-      <c r="E295" s="304"/>
+      <c r="E295" s="308"/>
       <c r="F295" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G295" s="304" t="s">
+      <c r="G295" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H295" s="304"/>
+      <c r="H295" s="308"/>
     </row>
     <row r="296" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B296" s="146"/>
       <c r="C296" s="145"/>
-      <c r="D296" s="304" t="s">
+      <c r="D296" s="308" t="s">
         <v>575</v>
       </c>
-      <c r="E296" s="304"/>
+      <c r="E296" s="308"/>
       <c r="F296" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G296" s="304" t="s">
+      <c r="G296" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H296" s="304"/>
+      <c r="H296" s="308"/>
     </row>
     <row r="298" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B298" s="132" t="s">
@@ -13168,7 +13208,7 @@
       </c>
     </row>
     <row r="300" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B300" s="356" t="s">
+      <c r="B300" s="309" t="s">
         <v>474</v>
       </c>
       <c r="C300" s="292" t="s">
@@ -13176,13 +13216,13 @@
       </c>
     </row>
     <row r="301" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B301" s="356"/>
+      <c r="B301" s="309"/>
       <c r="C301" s="292" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="302" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B302" s="356" t="s">
+      <c r="B302" s="309" t="s">
         <v>579</v>
       </c>
       <c r="C302" s="292" t="s">
@@ -13190,7 +13230,7 @@
       </c>
     </row>
     <row r="303" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B303" s="356"/>
+      <c r="B303" s="309"/>
       <c r="C303" s="292" t="s">
         <v>566</v>
       </c>
@@ -13210,62 +13250,62 @@
     </row>
     <row r="306" spans="1:15" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="215"/>
-      <c r="B306" s="364" t="s">
+      <c r="B306" s="326" t="s">
         <v>582</v>
       </c>
-      <c r="C306" s="364"/>
+      <c r="C306" s="326"/>
       <c r="D306" s="216" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A307" s="215"/>
-      <c r="B307" s="364"/>
-      <c r="C307" s="364"/>
+      <c r="B307" s="326"/>
+      <c r="C307" s="326"/>
       <c r="D307" s="216" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A308" s="215"/>
-      <c r="B308" s="364" t="s">
+      <c r="B308" s="326" t="s">
         <v>583</v>
       </c>
-      <c r="C308" s="364"/>
+      <c r="C308" s="326"/>
       <c r="D308" s="216" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A309" s="215"/>
-      <c r="B309" s="364"/>
-      <c r="C309" s="364"/>
+      <c r="B309" s="326"/>
+      <c r="C309" s="326"/>
       <c r="D309" s="216" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A310" s="215"/>
-      <c r="B310" s="364" t="s">
+      <c r="B310" s="326" t="s">
         <v>584</v>
       </c>
-      <c r="C310" s="364"/>
+      <c r="C310" s="326"/>
       <c r="D310" s="216" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A311" s="215"/>
-      <c r="B311" s="364"/>
-      <c r="C311" s="364"/>
+      <c r="B311" s="326"/>
+      <c r="C311" s="326"/>
       <c r="D311" s="216" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A312" s="215"/>
-      <c r="B312" s="364"/>
-      <c r="C312" s="364"/>
+      <c r="B312" s="326"/>
+      <c r="C312" s="326"/>
       <c r="D312" s="216" t="s">
         <v>586</v>
       </c>
@@ -13358,7 +13398,7 @@
       <c r="J327" s="300"/>
     </row>
     <row r="328" spans="1:15" ht="12" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B328" s="350" t="s">
+      <c r="B328" s="327" t="s">
         <v>378</v>
       </c>
       <c r="C328" s="138" t="s">
@@ -13376,7 +13416,7 @@
       </c>
     </row>
     <row r="329" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B329" s="350"/>
+      <c r="B329" s="327"/>
       <c r="C329" s="138" t="s">
         <v>599</v>
       </c>
@@ -13392,7 +13432,7 @@
       </c>
     </row>
     <row r="330" spans="1:15" ht="12" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B330" s="350"/>
+      <c r="B330" s="327"/>
       <c r="C330" s="138" t="s">
         <v>600</v>
       </c>
@@ -13408,7 +13448,7 @@
       </c>
     </row>
     <row r="331" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B331" s="350"/>
+      <c r="B331" s="327"/>
       <c r="C331" s="218" t="s">
         <v>601</v>
       </c>
@@ -13424,7 +13464,7 @@
       </c>
     </row>
     <row r="332" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B332" s="350"/>
+      <c r="B332" s="327"/>
       <c r="C332" s="138" t="s">
         <v>602</v>
       </c>
@@ -13458,7 +13498,7 @@
       </c>
     </row>
     <row r="334" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B334" s="350" t="s">
+      <c r="B334" s="327" t="s">
         <v>605</v>
       </c>
       <c r="C334" s="298" t="s">
@@ -13476,8 +13516,8 @@
       </c>
     </row>
     <row r="335" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B335" s="365"/>
-      <c r="C335" s="366" t="s">
+      <c r="B335" s="328"/>
+      <c r="C335" s="329" t="s">
         <v>607</v>
       </c>
       <c r="D335" s="138" t="s">
@@ -13489,13 +13529,16 @@
       <c r="H335" s="141"/>
       <c r="I335" s="141"/>
       <c r="J335" s="142"/>
+      <c r="K335" s="152" t="s">
+        <v>1281</v>
+      </c>
       <c r="O335" s="133" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="336" spans="1:15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B336" s="365"/>
-      <c r="C336" s="366"/>
+      <c r="B336" s="328"/>
+      <c r="C336" s="329"/>
       <c r="D336" s="138" t="s">
         <v>609</v>
       </c>
@@ -13510,8 +13553,8 @@
       </c>
     </row>
     <row r="337" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B337" s="365"/>
-      <c r="C337" s="366"/>
+      <c r="B337" s="328"/>
+      <c r="C337" s="329"/>
       <c r="D337" s="138" t="s">
         <v>610</v>
       </c>
@@ -13528,8 +13571,8 @@
       </c>
     </row>
     <row r="338" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="B338" s="365"/>
-      <c r="C338" s="366"/>
+      <c r="B338" s="328"/>
+      <c r="C338" s="329"/>
       <c r="D338" s="138" t="s">
         <v>612</v>
       </c>
@@ -14214,27 +14257,27 @@
       </c>
     </row>
     <row r="392" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B392" s="357" t="s">
+      <c r="B392" s="319" t="s">
         <v>670</v>
       </c>
-      <c r="C392" s="359" t="s">
+      <c r="C392" s="321" t="s">
         <v>563</v>
       </c>
-      <c r="D392" s="360"/>
+      <c r="D392" s="322"/>
       <c r="E392" s="224"/>
       <c r="F392" s="225"/>
     </row>
     <row r="393" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B393" s="358"/>
-      <c r="C393" s="361" t="s">
+      <c r="B393" s="320"/>
+      <c r="C393" s="323" t="s">
         <v>566</v>
       </c>
-      <c r="D393" s="362"/>
+      <c r="D393" s="324"/>
       <c r="E393" s="226"/>
       <c r="F393" s="225"/>
     </row>
     <row r="394" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B394" s="363" t="s">
+      <c r="B394" s="325" t="s">
         <v>671</v>
       </c>
       <c r="C394" s="216" t="s">
@@ -14248,7 +14291,7 @@
       </c>
     </row>
     <row r="395" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B395" s="363"/>
+      <c r="B395" s="325"/>
       <c r="C395" s="216" t="s">
         <v>674</v>
       </c>
@@ -14293,10 +14336,10 @@
       <c r="C401" s="301" t="s">
         <v>680</v>
       </c>
-      <c r="D401" s="352" t="s">
+      <c r="D401" s="310" t="s">
         <v>681</v>
       </c>
-      <c r="E401" s="352"/>
+      <c r="E401" s="310"/>
     </row>
     <row r="402" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B402" s="292" t="s">
@@ -14305,10 +14348,10 @@
       <c r="C402" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="D402" s="304" t="s">
+      <c r="D402" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="E402" s="304"/>
+      <c r="E402" s="308"/>
       <c r="O402" s="184"/>
     </row>
     <row r="403" spans="2:15" x14ac:dyDescent="0.15">
@@ -14318,10 +14361,10 @@
       <c r="C403" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="D403" s="304" t="s">
+      <c r="D403" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="E403" s="304"/>
+      <c r="E403" s="308"/>
     </row>
     <row r="404" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B404" s="141"/>
@@ -14335,21 +14378,21 @@
       </c>
     </row>
     <row r="406" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B406" s="352" t="s">
+      <c r="B406" s="310" t="s">
         <v>677</v>
       </c>
-      <c r="C406" s="370"/>
+      <c r="C406" s="311"/>
       <c r="D406" s="148" t="s">
         <v>682</v>
       </c>
       <c r="E406" s="158"/>
-      <c r="F406" s="371" t="s">
+      <c r="F406" s="312" t="s">
         <v>562</v>
       </c>
-      <c r="G406" s="373" t="s">
+      <c r="G406" s="314" t="s">
         <v>546</v>
       </c>
-      <c r="H406" s="374"/>
+      <c r="H406" s="315"/>
     </row>
     <row r="407" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B407" s="147" t="s">
@@ -14358,13 +14401,13 @@
       <c r="C407" s="147" t="s">
         <v>683</v>
       </c>
-      <c r="D407" s="353" t="s">
+      <c r="D407" s="318" t="s">
         <v>684</v>
       </c>
-      <c r="E407" s="353"/>
-      <c r="F407" s="372"/>
-      <c r="G407" s="375"/>
-      <c r="H407" s="376"/>
+      <c r="E407" s="318"/>
+      <c r="F407" s="313"/>
+      <c r="G407" s="316"/>
+      <c r="H407" s="317"/>
       <c r="O407" s="184"/>
     </row>
     <row r="408" spans="2:15" x14ac:dyDescent="0.15">
@@ -14374,17 +14417,17 @@
       <c r="C408" s="136" t="s">
         <v>685</v>
       </c>
-      <c r="D408" s="304" t="s">
+      <c r="D408" s="308" t="s">
         <v>686</v>
       </c>
-      <c r="E408" s="304"/>
+      <c r="E408" s="308"/>
       <c r="F408" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G408" s="304" t="s">
+      <c r="G408" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H408" s="304"/>
+      <c r="H408" s="308"/>
     </row>
     <row r="409" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B409" s="137" t="s">
@@ -14393,32 +14436,32 @@
       <c r="C409" s="136" t="s">
         <v>686</v>
       </c>
-      <c r="D409" s="304" t="s">
+      <c r="D409" s="308" t="s">
         <v>688</v>
       </c>
-      <c r="E409" s="304"/>
+      <c r="E409" s="308"/>
       <c r="F409" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G409" s="304" t="s">
+      <c r="G409" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H409" s="304"/>
+      <c r="H409" s="308"/>
     </row>
     <row r="410" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B410" s="146"/>
       <c r="C410" s="145"/>
-      <c r="D410" s="304" t="s">
+      <c r="D410" s="308" t="s">
         <v>689</v>
       </c>
-      <c r="E410" s="304"/>
+      <c r="E410" s="308"/>
       <c r="F410" s="292" t="s">
         <v>564</v>
       </c>
-      <c r="G410" s="304" t="s">
+      <c r="G410" s="308" t="s">
         <v>564</v>
       </c>
-      <c r="H410" s="304"/>
+      <c r="H410" s="308"/>
     </row>
     <row r="411" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B411" s="141"/>
@@ -14432,7 +14475,7 @@
       </c>
     </row>
     <row r="413" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B413" s="356" t="s">
+      <c r="B413" s="309" t="s">
         <v>474</v>
       </c>
       <c r="C413" s="292" t="s">
@@ -14440,13 +14483,13 @@
       </c>
     </row>
     <row r="414" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B414" s="356"/>
+      <c r="B414" s="309"/>
       <c r="C414" s="292" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="415" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B415" s="356" t="s">
+      <c r="B415" s="309" t="s">
         <v>692</v>
       </c>
       <c r="C415" s="292" t="s">
@@ -14454,7 +14497,7 @@
       </c>
     </row>
     <row r="416" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B416" s="356"/>
+      <c r="B416" s="309"/>
       <c r="C416" s="292" t="s">
         <v>693</v>
       </c>
@@ -14470,7 +14513,7 @@
       </c>
     </row>
     <row r="420" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B420" s="367" t="s">
+      <c r="B420" s="305" t="s">
         <v>389</v>
       </c>
       <c r="C420" s="292" t="s">
@@ -14479,19 +14522,19 @@
       <c r="O420" s="153"/>
     </row>
     <row r="421" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B421" s="368"/>
+      <c r="B421" s="306"/>
       <c r="C421" s="292" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="422" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B422" s="368"/>
+      <c r="B422" s="306"/>
       <c r="C422" s="292" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="423" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B423" s="369"/>
+      <c r="B423" s="307"/>
       <c r="C423" s="292" t="s">
         <v>698</v>
       </c>
@@ -14535,69 +14578,38 @@
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="B420:B423"/>
-    <mergeCell ref="D409:E409"/>
-    <mergeCell ref="G409:H409"/>
-    <mergeCell ref="D410:E410"/>
-    <mergeCell ref="G410:H410"/>
-    <mergeCell ref="B413:B414"/>
-    <mergeCell ref="B415:B416"/>
-    <mergeCell ref="B406:C406"/>
-    <mergeCell ref="F406:F407"/>
-    <mergeCell ref="G406:H407"/>
-    <mergeCell ref="D407:E407"/>
-    <mergeCell ref="D408:E408"/>
-    <mergeCell ref="G408:H408"/>
-    <mergeCell ref="D401:E401"/>
-    <mergeCell ref="D402:E402"/>
-    <mergeCell ref="D403:E403"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="C392:D392"/>
-    <mergeCell ref="C393:D393"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="B306:C307"/>
-    <mergeCell ref="B308:C309"/>
-    <mergeCell ref="B310:C312"/>
-    <mergeCell ref="B328:B332"/>
-    <mergeCell ref="B334:B338"/>
-    <mergeCell ref="C335:C338"/>
-    <mergeCell ref="D295:E295"/>
-    <mergeCell ref="G295:H295"/>
-    <mergeCell ref="D296:E296"/>
-    <mergeCell ref="G296:H296"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="D292:E292"/>
-    <mergeCell ref="G292:H292"/>
-    <mergeCell ref="D293:E293"/>
-    <mergeCell ref="G293:H293"/>
-    <mergeCell ref="D294:E294"/>
-    <mergeCell ref="G294:H294"/>
-    <mergeCell ref="C227:E227"/>
-    <mergeCell ref="F227:M227"/>
-    <mergeCell ref="B290:C290"/>
-    <mergeCell ref="G290:H290"/>
-    <mergeCell ref="D291:E291"/>
-    <mergeCell ref="G291:H291"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="F223:M223"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="F224:M224"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="F226:M226"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="F220:M220"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="F221:M221"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="F222:M222"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="F210:M210"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="F211:M211"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="F212:M212"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:N57"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:N62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:N63"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:N65"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="D58:E59"/>
+    <mergeCell ref="F58:N58"/>
+    <mergeCell ref="F59:N59"/>
+    <mergeCell ref="D60:E61"/>
+    <mergeCell ref="F60:N60"/>
+    <mergeCell ref="F61:N61"/>
     <mergeCell ref="D109:G109"/>
     <mergeCell ref="D110:G110"/>
     <mergeCell ref="C72:C73"/>
@@ -14615,38 +14627,69 @@
     <mergeCell ref="F70:N70"/>
     <mergeCell ref="D71:E71"/>
     <mergeCell ref="F71:N71"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:N65"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="D58:E59"/>
-    <mergeCell ref="F58:N58"/>
-    <mergeCell ref="F59:N59"/>
-    <mergeCell ref="D60:E61"/>
-    <mergeCell ref="F60:N60"/>
-    <mergeCell ref="F61:N61"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:N57"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:N62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:N63"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="F220:M220"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="F221:M221"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="F222:M222"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="C210:E210"/>
+    <mergeCell ref="F210:M210"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="F211:M211"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="F212:M212"/>
+    <mergeCell ref="C227:E227"/>
+    <mergeCell ref="F227:M227"/>
+    <mergeCell ref="B290:C290"/>
+    <mergeCell ref="G290:H290"/>
+    <mergeCell ref="D291:E291"/>
+    <mergeCell ref="G291:H291"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="F223:M223"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="F224:M224"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="F226:M226"/>
+    <mergeCell ref="D295:E295"/>
+    <mergeCell ref="G295:H295"/>
+    <mergeCell ref="D296:E296"/>
+    <mergeCell ref="G296:H296"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="D292:E292"/>
+    <mergeCell ref="G292:H292"/>
+    <mergeCell ref="D293:E293"/>
+    <mergeCell ref="G293:H293"/>
+    <mergeCell ref="D294:E294"/>
+    <mergeCell ref="G294:H294"/>
+    <mergeCell ref="D401:E401"/>
+    <mergeCell ref="D402:E402"/>
+    <mergeCell ref="D403:E403"/>
+    <mergeCell ref="B392:B393"/>
+    <mergeCell ref="C392:D392"/>
+    <mergeCell ref="C393:D393"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="B306:C307"/>
+    <mergeCell ref="B308:C309"/>
+    <mergeCell ref="B310:C312"/>
+    <mergeCell ref="B328:B332"/>
+    <mergeCell ref="B334:B338"/>
+    <mergeCell ref="C335:C338"/>
+    <mergeCell ref="B420:B423"/>
+    <mergeCell ref="D409:E409"/>
+    <mergeCell ref="G409:H409"/>
+    <mergeCell ref="D410:E410"/>
+    <mergeCell ref="G410:H410"/>
+    <mergeCell ref="B413:B414"/>
+    <mergeCell ref="B415:B416"/>
+    <mergeCell ref="B406:C406"/>
+    <mergeCell ref="F406:F407"/>
+    <mergeCell ref="G406:H407"/>
+    <mergeCell ref="D407:E407"/>
+    <mergeCell ref="D408:E408"/>
+    <mergeCell ref="G408:H408"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14656,7 +14699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M134"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
@@ -14669,46 +14712,46 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B2" s="395" t="s">
+      <c r="B2" s="378" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="395"/>
-      <c r="D2" s="382" t="s">
+      <c r="C2" s="378"/>
+      <c r="D2" s="379" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="384"/>
+      <c r="E2" s="380"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B3" s="395"/>
-      <c r="C3" s="395"/>
-      <c r="D3" s="382" t="s">
+      <c r="B3" s="378"/>
+      <c r="C3" s="378"/>
+      <c r="D3" s="379" t="s">
         <v>157</v>
       </c>
-      <c r="E3" s="384"/>
+      <c r="E3" s="380"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B4" s="382" t="s">
+      <c r="B4" s="379" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="383"/>
-      <c r="D4" s="383"/>
-      <c r="E4" s="384"/>
+      <c r="C4" s="392"/>
+      <c r="D4" s="392"/>
+      <c r="E4" s="380"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B5" s="385" t="s">
+      <c r="B5" s="393" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="386"/>
-      <c r="D5" s="386"/>
-      <c r="E5" s="387"/>
+      <c r="C5" s="394"/>
+      <c r="D5" s="394"/>
+      <c r="E5" s="395"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B6" s="385" t="s">
+      <c r="B6" s="393" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="386"/>
-      <c r="D6" s="386"/>
-      <c r="E6" s="387"/>
+      <c r="C6" s="394"/>
+      <c r="D6" s="394"/>
+      <c r="E6" s="395"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="19" t="s">
@@ -14787,11 +14830,11 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="72"/>
       <c r="B15" s="74"/>
-      <c r="C15" s="380" t="s">
+      <c r="C15" s="384" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="380"/>
-      <c r="E15" s="380"/>
+      <c r="D15" s="384"/>
+      <c r="E15" s="384"/>
       <c r="F15" s="253" t="s">
         <v>144</v>
       </c>
@@ -14800,11 +14843,11 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="72"/>
       <c r="B16" s="74"/>
-      <c r="C16" s="380" t="s">
+      <c r="C16" s="384" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="380"/>
-      <c r="E16" s="380"/>
+      <c r="D16" s="384"/>
+      <c r="E16" s="384"/>
       <c r="F16" s="253" t="s">
         <v>142</v>
       </c>
@@ -14869,11 +14912,11 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A21" s="72"/>
       <c r="B21" s="74"/>
-      <c r="C21" s="380" t="s">
+      <c r="C21" s="384" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="380"/>
-      <c r="E21" s="380"/>
+      <c r="D21" s="384"/>
+      <c r="E21" s="384"/>
       <c r="F21" s="253" t="s">
         <v>132</v>
       </c>
@@ -14882,11 +14925,11 @@
     <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A22" s="72"/>
       <c r="B22" s="74"/>
-      <c r="C22" s="380" t="s">
+      <c r="C22" s="384" t="s">
         <v>131</v>
       </c>
-      <c r="D22" s="380"/>
-      <c r="E22" s="380"/>
+      <c r="D22" s="384"/>
+      <c r="E22" s="384"/>
       <c r="F22" s="254" t="s">
         <v>129</v>
       </c>
@@ -14940,12 +14983,12 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A27" s="72"/>
-      <c r="B27" s="390" t="s">
+      <c r="B27" s="383" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="390"/>
-      <c r="D27" s="390"/>
-      <c r="E27" s="391" t="s">
+      <c r="C27" s="383"/>
+      <c r="D27" s="383"/>
+      <c r="E27" s="385" t="s">
         <v>126</v>
       </c>
       <c r="F27" s="19" t="s">
@@ -14960,7 +15003,7 @@
       </c>
       <c r="C28" s="83"/>
       <c r="D28" s="83"/>
-      <c r="E28" s="392"/>
+      <c r="E28" s="386"/>
       <c r="F28" s="72"/>
       <c r="G28" s="72"/>
     </row>
@@ -14971,7 +15014,7 @@
       </c>
       <c r="C29" s="264"/>
       <c r="D29" s="264"/>
-      <c r="E29" s="392"/>
+      <c r="E29" s="386"/>
       <c r="F29" s="85" t="s">
         <v>123</v>
       </c>
@@ -14986,7 +15029,7 @@
       </c>
       <c r="C30" s="83"/>
       <c r="D30" s="83"/>
-      <c r="E30" s="392"/>
+      <c r="E30" s="386"/>
       <c r="F30" s="82"/>
       <c r="G30" s="82"/>
       <c r="H30" s="81"/>
@@ -14998,7 +15041,7 @@
       </c>
       <c r="C31" s="83"/>
       <c r="D31" s="83"/>
-      <c r="E31" s="392"/>
+      <c r="E31" s="386"/>
       <c r="F31" s="82" t="s">
         <v>103</v>
       </c>
@@ -15012,7 +15055,7 @@
       </c>
       <c r="C32" s="83"/>
       <c r="D32" s="83"/>
-      <c r="E32" s="392"/>
+      <c r="E32" s="386"/>
       <c r="F32" s="82"/>
       <c r="G32" s="82"/>
       <c r="H32" s="81"/>
@@ -15024,7 +15067,7 @@
       </c>
       <c r="C33" s="83"/>
       <c r="D33" s="83"/>
-      <c r="E33" s="392"/>
+      <c r="E33" s="386"/>
       <c r="F33" s="82" t="s">
         <v>115</v>
       </c>
@@ -15038,7 +15081,7 @@
       </c>
       <c r="C34" s="83"/>
       <c r="D34" s="83"/>
-      <c r="E34" s="392"/>
+      <c r="E34" s="386"/>
       <c r="F34" s="82"/>
       <c r="G34" s="82"/>
       <c r="H34" s="81"/>
@@ -15050,7 +15093,7 @@
       </c>
       <c r="C35" s="83"/>
       <c r="D35" s="83"/>
-      <c r="E35" s="393"/>
+      <c r="E35" s="387"/>
       <c r="F35" s="82" t="s">
         <v>115</v>
       </c>
@@ -15130,10 +15173,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A42" s="72"/>
-      <c r="B42" s="388" t="s">
+      <c r="B42" s="396" t="s">
         <v>109</v>
       </c>
-      <c r="C42" s="388"/>
+      <c r="C42" s="396"/>
       <c r="D42" s="381" t="s">
         <v>108</v>
       </c>
@@ -15145,8 +15188,8 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A43" s="72"/>
-      <c r="B43" s="388"/>
-      <c r="C43" s="388"/>
+      <c r="B43" s="396"/>
+      <c r="C43" s="396"/>
       <c r="D43" s="381" t="s">
         <v>93</v>
       </c>
@@ -15156,8 +15199,8 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A44" s="72"/>
-      <c r="B44" s="388"/>
-      <c r="C44" s="388"/>
+      <c r="B44" s="396"/>
+      <c r="C44" s="396"/>
       <c r="D44" s="381" t="s">
         <v>106</v>
       </c>
@@ -15167,8 +15210,8 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A45" s="72"/>
-      <c r="B45" s="388"/>
-      <c r="C45" s="388"/>
+      <c r="B45" s="396"/>
+      <c r="C45" s="396"/>
       <c r="D45" s="381" t="s">
         <v>105</v>
       </c>
@@ -15178,8 +15221,8 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A46" s="72"/>
-      <c r="B46" s="388"/>
-      <c r="C46" s="388"/>
+      <c r="B46" s="396"/>
+      <c r="C46" s="396"/>
       <c r="D46" s="381" t="s">
         <v>104</v>
       </c>
@@ -15191,10 +15234,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A47" s="72"/>
-      <c r="B47" s="394" t="s">
+      <c r="B47" s="388" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="394"/>
+      <c r="C47" s="388"/>
       <c r="D47" s="381" t="s">
         <v>101</v>
       </c>
@@ -15208,8 +15251,8 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A48" s="72"/>
-      <c r="B48" s="394"/>
-      <c r="C48" s="394"/>
+      <c r="B48" s="388"/>
+      <c r="C48" s="388"/>
       <c r="D48" s="381" t="s">
         <v>93</v>
       </c>
@@ -15221,8 +15264,8 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49" s="72"/>
-      <c r="B49" s="394"/>
-      <c r="C49" s="394"/>
+      <c r="B49" s="388"/>
+      <c r="C49" s="388"/>
       <c r="D49" s="381" t="s">
         <v>99</v>
       </c>
@@ -15232,8 +15275,8 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50" s="72"/>
-      <c r="B50" s="394"/>
-      <c r="C50" s="394"/>
+      <c r="B50" s="388"/>
+      <c r="C50" s="388"/>
       <c r="D50" s="381" t="s">
         <v>98</v>
       </c>
@@ -15243,8 +15286,8 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51" s="72"/>
-      <c r="B51" s="394"/>
-      <c r="C51" s="394"/>
+      <c r="B51" s="388"/>
+      <c r="C51" s="388"/>
       <c r="D51" s="381" t="s">
         <v>97</v>
       </c>
@@ -15274,10 +15317,10 @@
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B55" s="389" t="s">
+      <c r="B55" s="382" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="389"/>
+      <c r="C55" s="382"/>
       <c r="D55" s="60" t="s">
         <v>93</v>
       </c>
@@ -15309,7 +15352,7 @@
       </c>
       <c r="E58" s="62"/>
       <c r="F58" s="61"/>
-      <c r="G58" s="377" t="s">
+      <c r="G58" s="389" t="s">
         <v>88</v>
       </c>
     </row>
@@ -15321,7 +15364,7 @@
       </c>
       <c r="E59" s="62"/>
       <c r="F59" s="61"/>
-      <c r="G59" s="378"/>
+      <c r="G59" s="390"/>
       <c r="H59" s="64"/>
       <c r="I59" s="64"/>
       <c r="J59" s="64"/>
@@ -15339,7 +15382,7 @@
       </c>
       <c r="E60" s="62"/>
       <c r="F60" s="61"/>
-      <c r="G60" s="378"/>
+      <c r="G60" s="390"/>
       <c r="H60" s="64"/>
       <c r="I60" s="65"/>
       <c r="J60" s="64"/>
@@ -15355,7 +15398,7 @@
       <c r="D61" s="62"/>
       <c r="E61" s="62"/>
       <c r="F61" s="61"/>
-      <c r="G61" s="379"/>
+      <c r="G61" s="391"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B62" s="59"/>
@@ -15373,13 +15416,13 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B65" s="389" t="s">
+      <c r="B65" s="382" t="s">
         <v>82</v>
       </c>
-      <c r="C65" s="389"/>
-      <c r="D65" s="389"/>
-      <c r="E65" s="389"/>
-      <c r="F65" s="389"/>
+      <c r="C65" s="382"/>
+      <c r="D65" s="382"/>
+      <c r="E65" s="382"/>
+      <c r="F65" s="382"/>
       <c r="G65" s="60" t="s">
         <v>81</v>
       </c>
@@ -15966,11 +16009,20 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="G58:G61"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="B42:C46"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C17:E17"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="C22:E22"/>
@@ -15987,20 +16039,11 @@
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D48:E48"/>
-    <mergeCell ref="G58:G61"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="B42:C46"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16009,7 +16052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O102"/>
   <sheetFormatPr defaultRowHeight="11.25" outlineLevelRow="1" x14ac:dyDescent="0.15"/>
   <cols>
@@ -16085,13 +16128,13 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="67.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="408" t="s">
+      <c r="A6" s="414" t="s">
         <v>220</v>
       </c>
       <c r="B6" s="100" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="410" t="b">
+      <c r="C6" s="416" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="99"/>
@@ -16101,11 +16144,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A7" s="409"/>
+      <c r="A7" s="415"/>
       <c r="B7" s="100" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="411"/>
+      <c r="C7" s="417"/>
       <c r="D7" s="99"/>
       <c r="E7" s="102"/>
       <c r="F7" s="89" t="s">
@@ -16113,13 +16156,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="101.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="408" t="s">
+      <c r="A8" s="414" t="s">
         <v>215</v>
       </c>
       <c r="B8" s="111" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="410" t="s">
+      <c r="C8" s="416" t="s">
         <v>213</v>
       </c>
       <c r="D8" s="110"/>
@@ -16132,11 +16175,11 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="78.75" x14ac:dyDescent="0.15">
-      <c r="A9" s="415"/>
+      <c r="A9" s="423"/>
       <c r="B9" s="109" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="416"/>
+      <c r="C9" s="424"/>
       <c r="D9" s="108"/>
       <c r="E9" s="107"/>
       <c r="F9" s="106" t="s">
@@ -16145,10 +16188,10 @@
       <c r="G9" s="89" t="s">
         <v>208</v>
       </c>
-      <c r="I9" s="396" t="s">
+      <c r="I9" s="428" t="s">
         <v>207</v>
       </c>
-      <c r="J9" s="396"/>
+      <c r="J9" s="428"/>
       <c r="K9" s="105" t="s">
         <v>206</v>
       </c>
@@ -16184,117 +16227,117 @@
       <c r="E11" s="99"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A13" s="397" t="s">
+      <c r="A13" s="421" t="s">
         <v>1173</v>
       </c>
-      <c r="B13" s="397" t="s">
+      <c r="B13" s="421" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="398" t="s">
+      <c r="C13" s="422" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="398"/>
-      <c r="E13" s="398"/>
-      <c r="F13" s="402" t="s">
+      <c r="D13" s="422"/>
+      <c r="E13" s="422"/>
+      <c r="F13" s="432" t="s">
         <v>198</v>
       </c>
-      <c r="G13" s="403"/>
-      <c r="H13" s="403"/>
+      <c r="G13" s="433"/>
+      <c r="H13" s="433"/>
     </row>
     <row r="14" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="397"/>
-      <c r="B14" s="397"/>
-      <c r="C14" s="412" t="s">
+      <c r="A14" s="421"/>
+      <c r="B14" s="421"/>
+      <c r="C14" s="418" t="s">
         <v>197</v>
       </c>
-      <c r="D14" s="413"/>
-      <c r="E14" s="414"/>
-      <c r="F14" s="402"/>
-      <c r="G14" s="403"/>
-      <c r="H14" s="403"/>
+      <c r="D14" s="419"/>
+      <c r="E14" s="420"/>
+      <c r="F14" s="432"/>
+      <c r="G14" s="433"/>
+      <c r="H14" s="433"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A15" s="397"/>
-      <c r="B15" s="397"/>
-      <c r="C15" s="399"/>
-      <c r="D15" s="400"/>
-      <c r="E15" s="401"/>
+      <c r="A15" s="421"/>
+      <c r="B15" s="421"/>
+      <c r="C15" s="429"/>
+      <c r="D15" s="430"/>
+      <c r="E15" s="431"/>
       <c r="F15" s="89" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A16" s="397"/>
-      <c r="B16" s="397"/>
-      <c r="C16" s="398" t="s">
+      <c r="A16" s="421"/>
+      <c r="B16" s="421"/>
+      <c r="C16" s="422" t="s">
         <v>195</v>
       </c>
-      <c r="D16" s="398"/>
-      <c r="E16" s="398"/>
+      <c r="D16" s="422"/>
+      <c r="E16" s="422"/>
       <c r="F16" s="89" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="398" t="s">
+      <c r="A17" s="422" t="s">
         <v>193</v>
       </c>
-      <c r="B17" s="397" t="s">
+      <c r="B17" s="421" t="s">
         <v>192</v>
       </c>
-      <c r="C17" s="398" t="s">
+      <c r="C17" s="422" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="398"/>
-      <c r="E17" s="398"/>
-      <c r="F17" s="402" t="s">
+      <c r="D17" s="422"/>
+      <c r="E17" s="422"/>
+      <c r="F17" s="432" t="s">
         <v>190</v>
       </c>
-      <c r="G17" s="403"/>
-      <c r="H17" s="403"/>
+      <c r="G17" s="433"/>
+      <c r="H17" s="433"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A18" s="398"/>
-      <c r="B18" s="397"/>
-      <c r="C18" s="398" t="s">
+      <c r="A18" s="422"/>
+      <c r="B18" s="421"/>
+      <c r="C18" s="422" t="s">
         <v>189</v>
       </c>
-      <c r="D18" s="398"/>
-      <c r="E18" s="398"/>
-      <c r="F18" s="402"/>
-      <c r="G18" s="403"/>
-      <c r="H18" s="403"/>
+      <c r="D18" s="422"/>
+      <c r="E18" s="422"/>
+      <c r="F18" s="432"/>
+      <c r="G18" s="433"/>
+      <c r="H18" s="433"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A19" s="398"/>
-      <c r="B19" s="397"/>
-      <c r="C19" s="417"/>
-      <c r="D19" s="418"/>
-      <c r="E19" s="419"/>
+      <c r="A19" s="422"/>
+      <c r="B19" s="421"/>
+      <c r="C19" s="425"/>
+      <c r="D19" s="426"/>
+      <c r="E19" s="427"/>
       <c r="F19" s="89" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A20" s="398"/>
-      <c r="B20" s="397"/>
-      <c r="C20" s="398" t="s">
+      <c r="A20" s="422"/>
+      <c r="B20" s="421"/>
+      <c r="C20" s="422" t="s">
         <v>187</v>
       </c>
-      <c r="D20" s="398"/>
-      <c r="E20" s="398"/>
+      <c r="D20" s="422"/>
+      <c r="E20" s="422"/>
       <c r="F20" s="89" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A21" s="404" t="s">
+      <c r="A21" s="410" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="405"/>
-      <c r="C21" s="406"/>
-      <c r="D21" s="406"/>
-      <c r="E21" s="407"/>
+      <c r="B21" s="411"/>
+      <c r="C21" s="412"/>
+      <c r="D21" s="412"/>
+      <c r="E21" s="413"/>
       <c r="F21" s="89" t="s">
         <v>184</v>
       </c>
@@ -16372,35 +16415,35 @@
       <c r="B31" s="96" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="421" t="s">
+      <c r="C31" s="408" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="421"/>
+      <c r="D31" s="408"/>
     </row>
     <row r="32" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="95"/>
-      <c r="B32" s="420" t="s">
+      <c r="B32" s="407" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="422" t="s">
+      <c r="C32" s="409" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="422"/>
+      <c r="D32" s="409"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" s="95"/>
-      <c r="B33" s="420"/>
-      <c r="C33" s="422" t="s">
+      <c r="B33" s="407"/>
+      <c r="C33" s="409" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="422"/>
+      <c r="D33" s="409"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="B34" s="420"/>
-      <c r="C34" s="422" t="s">
+      <c r="B34" s="407"/>
+      <c r="C34" s="409" t="s">
         <v>169</v>
       </c>
-      <c r="D34" s="422"/>
+      <c r="D34" s="409"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" s="89" t="s">
@@ -16519,7 +16562,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C55" s="423" t="s">
+      <c r="C55" s="399" t="s">
         <v>252</v>
       </c>
       <c r="D55" s="266" t="s">
@@ -16530,13 +16573,13 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C56" s="424"/>
+      <c r="C56" s="402"/>
       <c r="D56" s="266" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C57" s="425"/>
+      <c r="C57" s="400"/>
       <c r="D57" s="266" t="s">
         <v>255</v>
       </c>
@@ -16563,10 +16606,10 @@
       <c r="E61" s="116" t="s">
         <v>259</v>
       </c>
-      <c r="F61" s="426" t="s">
+      <c r="F61" s="403" t="s">
         <v>260</v>
       </c>
-      <c r="G61" s="427"/>
+      <c r="G61" s="404"/>
       <c r="H61" s="116" t="s">
         <v>261</v>
       </c>
@@ -16579,49 +16622,49 @@
       <c r="E62" s="118" t="s">
         <v>263</v>
       </c>
-      <c r="F62" s="428" t="s">
+      <c r="F62" s="405" t="s">
         <v>263</v>
       </c>
-      <c r="G62" s="429"/>
+      <c r="G62" s="406"/>
       <c r="H62" s="116" t="s">
         <v>263</v>
       </c>
       <c r="I62" s="119"/>
     </row>
     <row r="63" spans="1:9" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C63" s="430" t="s">
+      <c r="C63" s="397" t="s">
         <v>264</v>
       </c>
-      <c r="D63" s="423" t="s">
+      <c r="D63" s="399" t="s">
         <v>265</v>
       </c>
-      <c r="E63" s="431" t="s">
+      <c r="E63" s="401" t="s">
         <v>263</v>
       </c>
       <c r="F63" s="118" t="s">
         <v>266</v>
       </c>
       <c r="G63" s="118"/>
-      <c r="H63" s="423" t="s">
+      <c r="H63" s="399" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C64" s="430"/>
-      <c r="D64" s="425"/>
-      <c r="E64" s="431"/>
+      <c r="C64" s="397"/>
+      <c r="D64" s="400"/>
+      <c r="E64" s="401"/>
       <c r="F64" s="118" t="s">
         <v>267</v>
       </c>
       <c r="G64" s="118"/>
-      <c r="H64" s="425"/>
+      <c r="H64" s="400"/>
     </row>
     <row r="65" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C65" s="430"/>
-      <c r="D65" s="431" t="s">
+      <c r="C65" s="397"/>
+      <c r="D65" s="401" t="s">
         <v>263</v>
       </c>
-      <c r="E65" s="431" t="s">
+      <c r="E65" s="401" t="s">
         <v>263</v>
       </c>
       <c r="F65" s="118" t="s">
@@ -16633,9 +16676,9 @@
       </c>
     </row>
     <row r="66" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C66" s="430"/>
-      <c r="D66" s="431"/>
-      <c r="E66" s="431"/>
+      <c r="C66" s="397"/>
+      <c r="D66" s="401"/>
+      <c r="E66" s="401"/>
       <c r="F66" s="118" t="s">
         <v>268</v>
       </c>
@@ -16649,31 +16692,31 @@
       <c r="G67" s="120"/>
     </row>
     <row r="68" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C68" s="432" t="s">
+      <c r="C68" s="398" t="s">
         <v>269</v>
       </c>
-      <c r="D68" s="432"/>
-      <c r="E68" s="432"/>
+      <c r="D68" s="398"/>
+      <c r="E68" s="398"/>
       <c r="F68" s="116" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="69" spans="2:8" s="115" customFormat="1" ht="13.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C69" s="432" t="s">
+      <c r="C69" s="398" t="s">
         <v>264</v>
       </c>
-      <c r="D69" s="432"/>
-      <c r="E69" s="432"/>
+      <c r="D69" s="398"/>
+      <c r="E69" s="398"/>
       <c r="F69" s="116" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="70" spans="2:8" s="115" customFormat="1" ht="13.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C70" s="432" t="s">
+      <c r="C70" s="398" t="s">
         <v>262</v>
       </c>
-      <c r="D70" s="432"/>
-      <c r="E70" s="432"/>
+      <c r="D70" s="398"/>
+      <c r="E70" s="398"/>
       <c r="F70" s="116" t="s">
         <v>265</v>
       </c>
@@ -16702,10 +16745,10 @@
       </c>
     </row>
     <row r="74" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C74" s="430" t="s">
+      <c r="C74" s="397" t="s">
         <v>264</v>
       </c>
-      <c r="D74" s="432" t="s">
+      <c r="D74" s="398" t="s">
         <v>265</v>
       </c>
       <c r="E74" s="116" t="s">
@@ -16716,8 +16759,8 @@
       </c>
     </row>
     <row r="75" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C75" s="430"/>
-      <c r="D75" s="432"/>
+      <c r="C75" s="397"/>
+      <c r="D75" s="398"/>
       <c r="E75" s="116" t="s">
         <v>262</v>
       </c>
@@ -16744,10 +16787,10 @@
       </c>
     </row>
     <row r="78" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="430" t="s">
+      <c r="C78" s="397" t="s">
         <v>264</v>
       </c>
-      <c r="D78" s="432" t="s">
+      <c r="D78" s="398" t="s">
         <v>265</v>
       </c>
       <c r="E78" s="116" t="s">
@@ -16758,8 +16801,8 @@
       </c>
     </row>
     <row r="79" spans="2:8" s="115" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="430"/>
-      <c r="D79" s="432"/>
+      <c r="C79" s="397"/>
+      <c r="D79" s="398"/>
       <c r="E79" s="116" t="s">
         <v>262</v>
       </c>
@@ -16937,27 +16980,15 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="F17:H18"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:C7"/>
@@ -16969,15 +17000,27 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="F17:H18"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16987,7 +17030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P851"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18284,14 +18327,14 @@
         <v>858</v>
       </c>
       <c r="D217" s="437"/>
-      <c r="E217" s="433" t="s">
+      <c r="E217" s="438" t="s">
         <v>859</v>
       </c>
-      <c r="F217" s="433"/>
-      <c r="G217" s="433"/>
-      <c r="H217" s="433"/>
-      <c r="I217" s="433"/>
-      <c r="J217" s="433"/>
+      <c r="F217" s="438"/>
+      <c r="G217" s="438"/>
+      <c r="H217" s="438"/>
+      <c r="I217" s="438"/>
+      <c r="J217" s="438"/>
     </row>
     <row r="218" spans="1:11" s="120" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B218" s="120" t="s">
@@ -19443,28 +19486,28 @@
         <v>933</v>
       </c>
       <c r="D406" s="436"/>
-      <c r="E406" s="433" t="s">
+      <c r="E406" s="438" t="s">
         <v>934</v>
       </c>
-      <c r="F406" s="433"/>
-      <c r="G406" s="433"/>
-      <c r="H406" s="433"/>
-      <c r="I406" s="433"/>
-      <c r="J406" s="433"/>
-      <c r="K406" s="433"/>
-      <c r="L406" s="433"/>
+      <c r="F406" s="438"/>
+      <c r="G406" s="438"/>
+      <c r="H406" s="438"/>
+      <c r="I406" s="438"/>
+      <c r="J406" s="438"/>
+      <c r="K406" s="438"/>
+      <c r="L406" s="438"/>
     </row>
     <row r="407" spans="2:12" s="120" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C407" s="436"/>
       <c r="D407" s="436"/>
-      <c r="E407" s="433"/>
-      <c r="F407" s="433"/>
-      <c r="G407" s="433"/>
-      <c r="H407" s="433"/>
-      <c r="I407" s="433"/>
-      <c r="J407" s="433"/>
-      <c r="K407" s="433"/>
-      <c r="L407" s="433"/>
+      <c r="E407" s="438"/>
+      <c r="F407" s="438"/>
+      <c r="G407" s="438"/>
+      <c r="H407" s="438"/>
+      <c r="I407" s="438"/>
+      <c r="J407" s="438"/>
+      <c r="K407" s="438"/>
+      <c r="L407" s="438"/>
     </row>
     <row r="408" spans="2:12" s="120" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B408" s="120" t="s">
@@ -19563,32 +19606,32 @@
       <c r="L421" s="436"/>
     </row>
     <row r="422" spans="1:12" s="120" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C422" s="434" t="s">
+      <c r="C422" s="440" t="s">
         <v>1005</v>
       </c>
-      <c r="D422" s="434"/>
-      <c r="E422" s="433" t="s">
+      <c r="D422" s="440"/>
+      <c r="E422" s="438" t="s">
         <v>941</v>
       </c>
-      <c r="F422" s="433"/>
-      <c r="G422" s="433"/>
-      <c r="H422" s="433"/>
-      <c r="I422" s="433"/>
-      <c r="J422" s="433"/>
-      <c r="K422" s="433"/>
-      <c r="L422" s="433"/>
+      <c r="F422" s="438"/>
+      <c r="G422" s="438"/>
+      <c r="H422" s="438"/>
+      <c r="I422" s="438"/>
+      <c r="J422" s="438"/>
+      <c r="K422" s="438"/>
+      <c r="L422" s="438"/>
     </row>
     <row r="423" spans="1:12" s="120" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C423" s="434"/>
-      <c r="D423" s="434"/>
-      <c r="E423" s="433"/>
-      <c r="F423" s="433"/>
-      <c r="G423" s="433"/>
-      <c r="H423" s="433"/>
-      <c r="I423" s="433"/>
-      <c r="J423" s="433"/>
-      <c r="K423" s="433"/>
-      <c r="L423" s="433"/>
+      <c r="C423" s="440"/>
+      <c r="D423" s="440"/>
+      <c r="E423" s="438"/>
+      <c r="F423" s="438"/>
+      <c r="G423" s="438"/>
+      <c r="H423" s="438"/>
+      <c r="I423" s="438"/>
+      <c r="J423" s="438"/>
+      <c r="K423" s="438"/>
+      <c r="L423" s="438"/>
     </row>
     <row r="424" spans="1:12" s="120" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B424" s="120" t="s">
@@ -19993,32 +20036,32 @@
       </c>
     </row>
     <row r="502" spans="1:10" s="120" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C502" s="435" t="s">
+      <c r="C502" s="439" t="s">
         <v>378</v>
       </c>
-      <c r="D502" s="435"/>
-      <c r="E502" s="435" t="s">
+      <c r="D502" s="439"/>
+      <c r="E502" s="439" t="s">
         <v>857</v>
       </c>
-      <c r="F502" s="435"/>
-      <c r="G502" s="435"/>
-      <c r="H502" s="435"/>
-      <c r="I502" s="435"/>
-      <c r="J502" s="435"/>
+      <c r="F502" s="439"/>
+      <c r="G502" s="439"/>
+      <c r="H502" s="439"/>
+      <c r="I502" s="439"/>
+      <c r="J502" s="439"/>
     </row>
     <row r="503" spans="1:10" s="120" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C503" s="433" t="s">
+      <c r="C503" s="438" t="s">
         <v>952</v>
       </c>
-      <c r="D503" s="433"/>
-      <c r="E503" s="433" t="s">
+      <c r="D503" s="438"/>
+      <c r="E503" s="438" t="s">
         <v>953</v>
       </c>
-      <c r="F503" s="433"/>
-      <c r="G503" s="433"/>
-      <c r="H503" s="433"/>
-      <c r="I503" s="433"/>
-      <c r="J503" s="433"/>
+      <c r="F503" s="438"/>
+      <c r="G503" s="438"/>
+      <c r="H503" s="438"/>
+      <c r="I503" s="438"/>
+      <c r="J503" s="438"/>
     </row>
     <row r="504" spans="1:10" s="120" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B504" s="120" t="s">
@@ -20068,32 +20111,32 @@
       </c>
     </row>
     <row r="510" spans="1:10" s="120" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C510" s="435" t="s">
+      <c r="C510" s="439" t="s">
         <v>378</v>
       </c>
-      <c r="D510" s="435"/>
-      <c r="E510" s="435" t="s">
+      <c r="D510" s="439"/>
+      <c r="E510" s="439" t="s">
         <v>857</v>
       </c>
-      <c r="F510" s="435"/>
-      <c r="G510" s="435"/>
-      <c r="H510" s="435"/>
-      <c r="I510" s="435"/>
-      <c r="J510" s="435"/>
+      <c r="F510" s="439"/>
+      <c r="G510" s="439"/>
+      <c r="H510" s="439"/>
+      <c r="I510" s="439"/>
+      <c r="J510" s="439"/>
     </row>
     <row r="511" spans="1:10" s="120" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C511" s="433" t="s">
+      <c r="C511" s="438" t="s">
         <v>957</v>
       </c>
-      <c r="D511" s="433"/>
-      <c r="E511" s="434" t="s">
+      <c r="D511" s="438"/>
+      <c r="E511" s="440" t="s">
         <v>958</v>
       </c>
-      <c r="F511" s="434"/>
-      <c r="G511" s="434"/>
-      <c r="H511" s="434"/>
-      <c r="I511" s="434"/>
-      <c r="J511" s="434"/>
+      <c r="F511" s="440"/>
+      <c r="G511" s="440"/>
+      <c r="H511" s="440"/>
+      <c r="I511" s="440"/>
+      <c r="J511" s="440"/>
     </row>
     <row r="512" spans="1:10" s="120" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B512" s="120" t="s">
@@ -20182,33 +20225,33 @@
       </c>
     </row>
     <row r="525" spans="1:14" s="120" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="C525" s="435" t="s">
+      <c r="C525" s="439" t="s">
         <v>378</v>
       </c>
-      <c r="D525" s="435"/>
-      <c r="E525" s="435" t="s">
+      <c r="D525" s="439"/>
+      <c r="E525" s="439" t="s">
         <v>857</v>
       </c>
-      <c r="F525" s="435"/>
-      <c r="G525" s="435"/>
-      <c r="H525" s="435"/>
-      <c r="I525" s="435"/>
-      <c r="J525" s="435"/>
+      <c r="F525" s="439"/>
+      <c r="G525" s="439"/>
+      <c r="H525" s="439"/>
+      <c r="I525" s="439"/>
+      <c r="J525" s="439"/>
       <c r="N525" s="251"/>
     </row>
     <row r="526" spans="1:14" s="120" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C526" s="434" t="s">
+      <c r="C526" s="440" t="s">
         <v>961</v>
       </c>
-      <c r="D526" s="434"/>
-      <c r="E526" s="433" t="s">
+      <c r="D526" s="440"/>
+      <c r="E526" s="438" t="s">
         <v>1012</v>
       </c>
-      <c r="F526" s="433"/>
-      <c r="G526" s="433"/>
-      <c r="H526" s="433"/>
-      <c r="I526" s="433"/>
-      <c r="J526" s="433"/>
+      <c r="F526" s="438"/>
+      <c r="G526" s="438"/>
+      <c r="H526" s="438"/>
+      <c r="I526" s="438"/>
+      <c r="J526" s="438"/>
       <c r="L526" s="251"/>
       <c r="M526" s="251"/>
     </row>
@@ -20644,62 +20687,62 @@
       <c r="L562" s="436"/>
     </row>
     <row r="563" spans="1:14" s="243" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C563" s="438" t="s">
+      <c r="C563" s="435" t="s">
         <v>1022</v>
       </c>
-      <c r="D563" s="438"/>
-      <c r="E563" s="438"/>
-      <c r="F563" s="438" t="s">
+      <c r="D563" s="435"/>
+      <c r="E563" s="435"/>
+      <c r="F563" s="435" t="s">
         <v>1023</v>
       </c>
-      <c r="G563" s="438"/>
-      <c r="H563" s="438"/>
-      <c r="I563" s="438"/>
-      <c r="J563" s="438"/>
-      <c r="K563" s="438"/>
-      <c r="L563" s="438"/>
+      <c r="G563" s="435"/>
+      <c r="H563" s="435"/>
+      <c r="I563" s="435"/>
+      <c r="J563" s="435"/>
+      <c r="K563" s="435"/>
+      <c r="L563" s="435"/>
     </row>
     <row r="564" spans="1:14" s="243" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C564" s="438" t="s">
+      <c r="C564" s="435" t="s">
         <v>1024</v>
       </c>
-      <c r="D564" s="438"/>
-      <c r="E564" s="438"/>
-      <c r="F564" s="438" t="s">
+      <c r="D564" s="435"/>
+      <c r="E564" s="435"/>
+      <c r="F564" s="435" t="s">
         <v>1025</v>
       </c>
-      <c r="G564" s="438"/>
-      <c r="H564" s="438"/>
-      <c r="I564" s="438"/>
-      <c r="J564" s="438"/>
-      <c r="K564" s="438"/>
-      <c r="L564" s="438"/>
+      <c r="G564" s="435"/>
+      <c r="H564" s="435"/>
+      <c r="I564" s="435"/>
+      <c r="J564" s="435"/>
+      <c r="K564" s="435"/>
+      <c r="L564" s="435"/>
     </row>
     <row r="565" spans="1:14" s="243" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C565" s="438" t="s">
+      <c r="C565" s="435" t="s">
         <v>1026</v>
       </c>
-      <c r="D565" s="438"/>
-      <c r="E565" s="438"/>
-      <c r="F565" s="438" t="s">
+      <c r="D565" s="435"/>
+      <c r="E565" s="435"/>
+      <c r="F565" s="435" t="s">
         <v>1027</v>
       </c>
-      <c r="G565" s="438"/>
-      <c r="H565" s="438"/>
-      <c r="I565" s="438"/>
-      <c r="J565" s="438"/>
-      <c r="K565" s="438"/>
-      <c r="L565" s="438"/>
+      <c r="G565" s="435"/>
+      <c r="H565" s="435"/>
+      <c r="I565" s="435"/>
+      <c r="J565" s="435"/>
+      <c r="K565" s="435"/>
+      <c r="L565" s="435"/>
       <c r="N565" s="247" t="s">
         <v>1042</v>
       </c>
     </row>
     <row r="566" spans="1:14" s="243" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C566" s="438" t="s">
+      <c r="C566" s="435" t="s">
         <v>1043</v>
       </c>
-      <c r="D566" s="438"/>
-      <c r="E566" s="438"/>
+      <c r="D566" s="435"/>
+      <c r="E566" s="435"/>
       <c r="F566" s="259" t="s">
         <v>1044</v>
       </c>
@@ -20729,20 +20772,20 @@
       <c r="N567" s="247"/>
     </row>
     <row r="568" spans="1:14" s="243" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C568" s="438" t="s">
+      <c r="C568" s="435" t="s">
         <v>1028</v>
       </c>
-      <c r="D568" s="438"/>
-      <c r="E568" s="438"/>
-      <c r="F568" s="438" t="s">
+      <c r="D568" s="435"/>
+      <c r="E568" s="435"/>
+      <c r="F568" s="435" t="s">
         <v>1029</v>
       </c>
-      <c r="G568" s="438"/>
-      <c r="H568" s="438"/>
-      <c r="I568" s="438"/>
-      <c r="J568" s="438"/>
-      <c r="K568" s="438"/>
-      <c r="L568" s="438"/>
+      <c r="G568" s="435"/>
+      <c r="H568" s="435"/>
+      <c r="I568" s="435"/>
+      <c r="J568" s="435"/>
+      <c r="K568" s="435"/>
+      <c r="L568" s="435"/>
     </row>
     <row r="569" spans="1:14" s="243" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="C569" s="251"/>
@@ -20875,36 +20918,36 @@
       <c r="N585" s="242"/>
     </row>
     <row r="586" spans="1:14" s="243" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C586" s="439" t="s">
+      <c r="C586" s="434" t="s">
         <v>961</v>
       </c>
-      <c r="D586" s="439"/>
-      <c r="E586" s="439"/>
-      <c r="F586" s="439" t="s">
+      <c r="D586" s="434"/>
+      <c r="E586" s="434"/>
+      <c r="F586" s="434" t="s">
         <v>1037</v>
       </c>
-      <c r="G586" s="439"/>
-      <c r="H586" s="439"/>
-      <c r="I586" s="439"/>
-      <c r="J586" s="439"/>
-      <c r="K586" s="439"/>
-      <c r="L586" s="439"/>
+      <c r="G586" s="434"/>
+      <c r="H586" s="434"/>
+      <c r="I586" s="434"/>
+      <c r="J586" s="434"/>
+      <c r="K586" s="434"/>
+      <c r="L586" s="434"/>
     </row>
     <row r="587" spans="1:14" s="243" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C587" s="439" t="s">
+      <c r="C587" s="434" t="s">
         <v>961</v>
       </c>
-      <c r="D587" s="439"/>
-      <c r="E587" s="439"/>
-      <c r="F587" s="439" t="s">
+      <c r="D587" s="434"/>
+      <c r="E587" s="434"/>
+      <c r="F587" s="434" t="s">
         <v>1038</v>
       </c>
-      <c r="G587" s="439"/>
-      <c r="H587" s="439"/>
-      <c r="I587" s="439"/>
-      <c r="J587" s="439"/>
-      <c r="K587" s="439"/>
-      <c r="L587" s="439"/>
+      <c r="G587" s="434"/>
+      <c r="H587" s="434"/>
+      <c r="I587" s="434"/>
+      <c r="J587" s="434"/>
+      <c r="K587" s="434"/>
+      <c r="L587" s="434"/>
     </row>
     <row r="588" spans="1:14" s="243" customFormat="1" x14ac:dyDescent="0.15">
       <c r="C588" s="243" t="s">
@@ -22416,29 +22459,12 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C586:E586"/>
-    <mergeCell ref="F586:L586"/>
-    <mergeCell ref="C587:E587"/>
-    <mergeCell ref="F587:L587"/>
-    <mergeCell ref="C566:E566"/>
-    <mergeCell ref="C565:E565"/>
-    <mergeCell ref="F565:L565"/>
-    <mergeCell ref="C568:E568"/>
-    <mergeCell ref="F568:L568"/>
-    <mergeCell ref="C585:E585"/>
-    <mergeCell ref="F585:L585"/>
-    <mergeCell ref="C562:E562"/>
-    <mergeCell ref="F562:L562"/>
-    <mergeCell ref="C563:E563"/>
-    <mergeCell ref="F563:L563"/>
-    <mergeCell ref="C564:E564"/>
-    <mergeCell ref="F564:L564"/>
-    <mergeCell ref="C216:D216"/>
-    <mergeCell ref="E216:J216"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="E217:J217"/>
-    <mergeCell ref="C235:D235"/>
-    <mergeCell ref="E235:J235"/>
+    <mergeCell ref="C511:D511"/>
+    <mergeCell ref="E511:J511"/>
+    <mergeCell ref="C525:D525"/>
+    <mergeCell ref="E525:J525"/>
+    <mergeCell ref="C526:D526"/>
+    <mergeCell ref="E526:J526"/>
     <mergeCell ref="C510:D510"/>
     <mergeCell ref="E510:J510"/>
     <mergeCell ref="C255:D255"/>
@@ -22453,12 +22479,29 @@
     <mergeCell ref="E502:J502"/>
     <mergeCell ref="C503:D503"/>
     <mergeCell ref="E503:J503"/>
-    <mergeCell ref="C511:D511"/>
-    <mergeCell ref="E511:J511"/>
-    <mergeCell ref="C525:D525"/>
-    <mergeCell ref="E525:J525"/>
-    <mergeCell ref="C526:D526"/>
-    <mergeCell ref="E526:J526"/>
+    <mergeCell ref="C216:D216"/>
+    <mergeCell ref="E216:J216"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="E217:J217"/>
+    <mergeCell ref="C235:D235"/>
+    <mergeCell ref="E235:J235"/>
+    <mergeCell ref="C562:E562"/>
+    <mergeCell ref="F562:L562"/>
+    <mergeCell ref="C563:E563"/>
+    <mergeCell ref="F563:L563"/>
+    <mergeCell ref="C564:E564"/>
+    <mergeCell ref="F564:L564"/>
+    <mergeCell ref="C565:E565"/>
+    <mergeCell ref="F565:L565"/>
+    <mergeCell ref="C568:E568"/>
+    <mergeCell ref="F568:L568"/>
+    <mergeCell ref="C585:E585"/>
+    <mergeCell ref="F585:L585"/>
+    <mergeCell ref="C586:E586"/>
+    <mergeCell ref="F586:L586"/>
+    <mergeCell ref="C587:E587"/>
+    <mergeCell ref="F587:L587"/>
+    <mergeCell ref="C566:E566"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22468,7 +22511,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
